--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484161_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484161_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1185</v>
+        <v>2.8562</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4665</v>
+        <v>4.2884</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.348</v>
+        <v>-1.4322</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5534</v>
@@ -610,13 +610,13 @@
         <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2295</v>
+        <v>-0.4918</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7141</v>
+        <v>0.1078</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5154</v>
+        <v>-0.5995</v>
       </c>
       <c r="V2" t="n">
         <v>4.8933</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6193</v>
+        <v>0.6536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.8562</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1745</v>
+        <v>-0.2026</v>
       </c>
       <c r="G3" t="n">
         <v>0.981</v>
@@ -688,13 +688,13 @@
         <v>0.1984</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8973</v>
+        <v>-0.863</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4364</v>
+        <v>-0.3741</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4609</v>
+        <v>-0.4889</v>
       </c>
       <c r="V3" t="n">
         <v>0.3373</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>I. DRIOUECH ELMRABET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1545</v>
+        <v>-0.3807</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1489</v>
+        <v>-0.0222</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3034</v>
+        <v>-0.3585</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1895</v>
+        <v>-0.0254</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4336</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6231</v>
+        <v>0.0402</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9253</v>
+        <v>0.0402</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7647</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1606</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1148</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3311</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7837</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.293</v>
+        <v>-0.0893</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2155</v>
+        <v>-0.0623</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0775</v>
+        <v>-0.0269</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1387</v>
+        <v>-0.266</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1387</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DRIOUECH ELMRABET</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4087</v>
+        <v>-0.7069</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0222</v>
+        <v>0.9051</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3865</v>
+        <v>-1.612</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0254</v>
+        <v>-0.1895</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.4336</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0402</v>
+        <v>-0.6231</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0402</v>
+        <v>1.9253</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.7647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>0.1606</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-2.1148</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-1.3311</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.7837</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1173</v>
+        <v>-0.2593</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0623</v>
+        <v>-0.0283</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.055</v>
+        <v>-0.2311</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>0.1387</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1569</v>
+        <v>-0.9163</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0235</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1804</v>
+        <v>-1.4329</v>
       </c>
       <c r="G6" t="n">
         <v>1.0439</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4235</v>
+        <v>-0.1828</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>0.1191</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0494</v>
+        <v>-0.3019</v>
       </c>
       <c r="V6" t="n">
         <v>0.6032</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8765</v>
+        <v>-1.5999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9538</v>
+        <v>-0.7894</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9227</v>
+        <v>-0.8105</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6995</v>
@@ -1000,13 +1000,13 @@
         <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8434</v>
+        <v>-0.5668</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3741</v>
+        <v>-0.2097</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4693</v>
+        <v>-0.3571</v>
       </c>
       <c r="V7" t="n">
         <v>-0.532</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5047</v>
+        <v>-3.014</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4306</v>
+        <v>0.0055</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9353</v>
+        <v>-3.0195</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2206</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0289</v>
+        <v>-0.4804</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3742</v>
+        <v>-0.0509</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3453</v>
+        <v>-0.4295</v>
       </c>
       <c r="V8" t="n">
         <v>0.8692</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>A. TARRIDA TORRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7297</v>
+        <v>-3.3204</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4983</v>
+        <v>-0.3534</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2313</v>
+        <v>-2.9671</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1884</v>
+        <v>-2.5646</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6687</v>
+        <v>-1.4516</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5196</v>
+        <v>-1.1129</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2543</v>
+        <v>0.0207</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7311</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4768</v>
+        <v>-0.5948</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4427</v>
+        <v>-2.5852</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.3999</v>
+        <v>-2.0671</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0428</v>
+        <v>-0.5182</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2164</v>
+        <v>-1.6168</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1699</v>
+        <v>-0.374</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0464</v>
+        <v>-1.2428</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4686</v>
+        <v>0.0675</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4012</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0.0675</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TARRIDA TORRES</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8059</v>
+        <v>-3.4599</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6424</v>
+        <v>-0.453</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1634</v>
+        <v>-3.0069</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5646</v>
+        <v>-3.1884</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4516</v>
+        <v>-1.6687</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1129</v>
+        <v>-1.5196</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0207</v>
+        <v>0.2543</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.7311</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5948</v>
+        <v>-0.4768</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5852</v>
+        <v>-3.4427</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0671</v>
+        <v>-2.3999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5182</v>
+        <v>-1.0428</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7935</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1023</v>
+        <v>-0.9466</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6631</v>
+        <v>-0.1246</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4392</v>
+        <v>-0.822</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0675</v>
+        <v>1.4686</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4012</v>
       </c>
       <c r="X10" t="n">
         <v>0.0675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7332</v>
+        <v>-3.93</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8723</v>
+        <v>-0.2374</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8609</v>
+        <v>-3.6926</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2583</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8797</v>
+        <v>-0.0765</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5498</v>
+        <v>0.0851</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3299</v>
+        <v>-0.1616</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9824</v>
+        <v>-6.2378</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7874</v>
+        <v>-1.0708</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.195</v>
+        <v>-5.167</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0779</v>
@@ -1390,13 +1390,13 @@
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.293</v>
+        <v>-0.5484</v>
       </c>
       <c r="T12" t="n">
-        <v>0.771</v>
+        <v>0.4876</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.064</v>
+        <v>-1.036</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6115</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.6147</v>
+        <v>-20.0561</v>
       </c>
       <c r="E13" t="n">
-        <v>2.087</v>
+        <v>3.6456</v>
       </c>
       <c r="F13" t="n">
-        <v>-23.7014</v>
+        <v>-23.7018</v>
       </c>
       <c r="G13" t="n">
         <v>-10.7527</v>
@@ -1441,13 +1441,13 @@
         <v>4.0161</v>
       </c>
       <c r="J13" t="n">
-        <v>9.051299999999999</v>
+        <v>9.051300000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>1.894</v>
+        <v>1.893999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>7.157</v>
+        <v>7.157000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-19.8039</v>
@@ -1468,10 +1468,10 @@
         <v>6.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.680499999999999</v>
+        <v>-6.121700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9831</v>
+        <v>-0.4243000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-5.6973</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.6319</v>
+        <v>9.898</v>
       </c>
       <c r="E14" t="n">
-        <v>10.2859</v>
+        <v>10.3879</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.654</v>
+        <v>-0.4899</v>
       </c>
       <c r="G14" t="n">
         <v>8.294499999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6989</v>
+        <v>0.965</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4876</v>
+        <v>0.5896</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2113</v>
+        <v>0.3754</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5437</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5132</v>
+        <v>4.4384</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0022</v>
+        <v>4.0939</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.489</v>
+        <v>0.3445</v>
       </c>
       <c r="G15" t="n">
-        <v>2.927</v>
+        <v>4.9515</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6796</v>
+        <v>3.0043</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7526</v>
+        <v>1.9473</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6847</v>
+        <v>4.97</v>
       </c>
       <c r="K15" t="n">
-        <v>3.524</v>
+        <v>2.9192</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1606</v>
+        <v>2.0508</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7577</v>
+        <v>-0.0184</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1556</v>
+        <v>0.0851</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9133</v>
+        <v>-0.1035</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7927</v>
+        <v>1.7727</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7775</v>
+        <v>1.1791</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0152</v>
+        <v>0.5936</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6032</v>
+        <v>-2.4842</v>
       </c>
       <c r="W15" t="n">
-        <v>0.532</v>
+        <v>-0.0713</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1352</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8882</v>
+        <v>4.3629</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0122</v>
+        <v>4.4718</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1239</v>
+        <v>-0.1089</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9515</v>
+        <v>2.927</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0043</v>
+        <v>3.6796</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9473</v>
+        <v>-0.7526</v>
       </c>
       <c r="J16" t="n">
-        <v>4.97</v>
+        <v>3.6847</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9192</v>
+        <v>3.524</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0508</v>
+        <v>0.1606</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0184</v>
+        <v>-0.7577</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0851</v>
+        <v>0.1556</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1035</v>
+        <v>-0.9133</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2225</v>
+        <v>1.6423</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0973</v>
+        <v>1.2471</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1252</v>
+        <v>0.3953</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4842</v>
+        <v>-0.6032</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0713</v>
+        <v>0.532</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4129</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4403</v>
+        <v>2.9504</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5114</v>
+        <v>3.6134</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0711</v>
+        <v>-0.663</v>
       </c>
       <c r="G17" t="n">
         <v>-0.08119999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9182</v>
+        <v>1.4284</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9467</v>
+        <v>1.0487</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0284</v>
+        <v>0.3797</v>
       </c>
       <c r="V17" t="n">
         <v>1.2065</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3274</v>
+        <v>1.4492</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0669</v>
+        <v>1.5932</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2604</v>
+        <v>-0.1441</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4282</v>
+        <v>-0.3752</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4839</v>
+        <v>0.156</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0557</v>
+        <v>-0.5312</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9398</v>
+        <v>0.0806</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4166</v>
+        <v>0.0806</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4768</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.4558</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9327</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4211</v>
+        <v>-0.5312</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1137</v>
+        <v>0.4195</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1191</v>
+        <v>0.3061</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9946</v>
+        <v>0.1133</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2065</v>
+        <v>1.2065</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.864</v>
+        <v>1.2721</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2266</v>
+        <v>0.6347</v>
       </c>
       <c r="F19" t="n">
         <v>0.6373</v>
@@ -1936,10 +1936,10 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2607</v>
+        <v>0.1474</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5611</v>
+        <v>-0.153</v>
       </c>
       <c r="U19" t="n">
         <v>0.3004</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7927999999999999</v>
+        <v>1.2126</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1851</v>
+        <v>0.373</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3923</v>
+        <v>0.8396</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3752</v>
+        <v>0.4282</v>
       </c>
       <c r="H20" t="n">
-        <v>0.156</v>
+        <v>0.4839</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5312</v>
+        <v>-0.0557</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0806</v>
+        <v>0.9398</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0806</v>
+        <v>1.4166</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.4768</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4558</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.9327</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5312</v>
+        <v>0.4211</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>1.9838</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2369</v>
+        <v>0.999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.102</v>
+        <v>0.4252</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1349</v>
+        <v>0.5738</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2065</v>
+        <v>-1.2065</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.0304</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1877</v>
+        <v>0.3918</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2772</v>
+        <v>-0.3613</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4924</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.403</v>
+        <v>0.5229</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1474</v>
+        <v>0.3514</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2556</v>
+        <v>0.1714</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3743</v>
+        <v>-0.1141</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9744</v>
+        <v>0.7703</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3487</v>
+        <v>-0.8845</v>
       </c>
       <c r="G22" t="n">
         <v>0.1745</v>
@@ -2170,13 +2170,13 @@
         <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5306</v>
+        <v>0.7907</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6349</v>
+        <v>0.4309</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1044</v>
+        <v>0.3598</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2777</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3481</v>
+        <v>-0.8307</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3377</v>
+        <v>-0.5968</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9896</v>
+        <v>-0.2339</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2963</v>
+        <v>-1.8392</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7105</v>
+        <v>0.2517</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5858</v>
+        <v>-2.091</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7766</v>
+        <v>-0.3981</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5794</v>
+        <v>0.2419</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1972</v>
+        <v>-0.64</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5198</v>
+        <v>-1.4412</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1312</v>
+        <v>0.0098</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3886</v>
+        <v>-1.4509</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.242</v>
+        <v>0.9409</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5611</v>
+        <v>0.5272</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3191</v>
+        <v>0.4137</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0313</v>
+        <v>-1.0139</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4131</v>
+        <v>-2.0316</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6182</v>
+        <v>1.0177</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8392</v>
+        <v>-2.2963</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2517</v>
+        <v>-0.7105</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.091</v>
+        <v>-1.5858</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3981</v>
+        <v>-1.7766</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2419</v>
+        <v>-0.5794</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.64</v>
+        <v>-1.1972</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4412</v>
+        <v>-0.5198</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0098</v>
+        <v>-0.1312</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4509</v>
+        <v>-0.3886</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2596</v>
+        <v>0.0921</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.289</v>
+        <v>-0.255</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0294</v>
+        <v>0.3471</v>
       </c>
       <c r="V24" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>21.6147</v>
+        <v>23.6553</v>
       </c>
       <c r="E25" t="n">
         <v>23.7016</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0871</v>
+        <v>-0.04649999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>10.7529</v>
@@ -2383,7 +2383,7 @@
         <v>16.6628</v>
       </c>
       <c r="L25" t="n">
-        <v>3.140899999999999</v>
+        <v>3.140900000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-9.0512</v>
@@ -2404,13 +2404,13 @@
         <v>13.8868</v>
       </c>
       <c r="S25" t="n">
-        <v>7.680400000000001</v>
+        <v>9.720899999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>5.6973</v>
+        <v>5.697299999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.9831</v>
+        <v>4.023499999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7618</v>
